--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136449396</v>
       </c>
       <c r="B18" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136449396</v>
       </c>
       <c r="B18" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136449396</v>
       </c>
       <c r="B18" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136449397</v>
       </c>
       <c r="B6" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136449396</v>
       </c>
       <c r="B18" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
